--- a/Output/039_51.2TB.xlsx
+++ b/Output/039_51.2TB.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="140">
   <si>
     <t>链接</t>
   </si>
@@ -28,244 +28,412 @@
     <t>Total File Size</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:ed8a21792cc5c85502649040536bbaa50ec52a75</t>
+    <t>magnet:?xt=urn:btih:0083ac9fed705e761b4565e88136c84c4d4534f9</t>
+  </si>
+  <si>
+    <t>FC2-PPV-4513600</t>
+  </si>
+  <si>
+    <t>2.90 GB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:00b19eb195da543d79bfe7aecf2fdd35919cf09b</t>
+  </si>
+  <si>
+    <t>FC2-PPV-3139256</t>
+  </si>
+  <si>
+    <t>7.49 GB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:00f017eb4fde0cb9c035622145dc39b909bf45ca</t>
+  </si>
+  <si>
+    <t>FC2-PPV-2660244</t>
+  </si>
+  <si>
+    <t>2.46 GB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0101c96e4289dbf19884f75a4d3f200c1fc713b9</t>
+  </si>
+  <si>
+    <t>FC2-PPV-4324199</t>
+  </si>
+  <si>
+    <t>6.01 GB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:010bb383cf5940d12e73152b1b4c747885f777fb</t>
+  </si>
+  <si>
+    <t>FC2-PPV-4330669</t>
+  </si>
+  <si>
+    <t>4.76 GB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:011248bea8ad8266d2c02cacf9c82c53acabd52a</t>
+  </si>
+  <si>
+    <t>FC2-PPV-2639856</t>
+  </si>
+  <si>
+    <t>2.52 GB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:014081a32c57f72aec36ab8acdab711702251a0b</t>
+  </si>
+  <si>
+    <t>FC2-PPV-3125448</t>
+  </si>
+  <si>
+    <t>788.16 MB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:014b36aa1f285dbc71c804ac270c8a88b15332f5</t>
+  </si>
+  <si>
+    <t>FC2-PPV-4416910</t>
+  </si>
+  <si>
+    <t>2.41 GB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0157d6c0c54ae42fbb7cb08fcfb4702ed92af7c4</t>
+  </si>
+  <si>
+    <t>FC2-PPV-4493206</t>
+  </si>
+  <si>
+    <t>6.94 GB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0159157fa518998fa15687581ceb90dc370267ca</t>
+  </si>
+  <si>
+    <t>FC2-PPV-3135454</t>
+  </si>
+  <si>
+    <t>6.16 GB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:017988c72f41c3352861246de40fdf4ec1da1926</t>
+  </si>
+  <si>
+    <t>FC2-PPV-4300514</t>
+  </si>
+  <si>
+    <t>4.35 GB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:01920920688e2d67f4504f01fc5c6c30337b68a7</t>
+  </si>
+  <si>
+    <t>FC2-PPV-4595191</t>
+  </si>
+  <si>
+    <t>14.34 GB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:01929c1851db090108f32c33bbdcc405474ff4ad</t>
+  </si>
+  <si>
+    <t>FC2-PPV-4576535</t>
+  </si>
+  <si>
+    <t>3.28 GB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:01b9982de8bd7ecfdfb4447b5f4c2929366eb39c</t>
+  </si>
+  <si>
+    <t>FC2-PPV-4356789</t>
+  </si>
+  <si>
+    <t>4.73 GB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:01bbae5ca3dd3a83ca0ff4b0b8bdfe023bb82ed7</t>
+  </si>
+  <si>
+    <t>FC2-PPV-4398557</t>
+  </si>
+  <si>
+    <t>6.10 GB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:01d04e0a40da9342871d82ab77eabe3c691f5ca7</t>
+  </si>
+  <si>
+    <t>FC2-PPV-2765740</t>
+  </si>
+  <si>
+    <t>1.72 GB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:01fc0800b3cd20ce597eb71894a52a9705351ebc</t>
+  </si>
+  <si>
+    <t>FC2-PPV-4474386</t>
+  </si>
+  <si>
+    <t>3.43 GB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:02cad57be1e7f122b2b0b9cbe3b931d2158cc1a8</t>
+  </si>
+  <si>
+    <t>FC2-PPV-2675548</t>
+  </si>
+  <si>
+    <t>5.61 GB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:02cf58594959fce64413d9c360013c31f9d9e834</t>
+  </si>
+  <si>
+    <t>FC2-PPV-4556221</t>
+  </si>
+  <si>
+    <t>4.31 GB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:02d357d271dd0ed4f7db9871d73c0957f28f0382</t>
+  </si>
+  <si>
+    <t>FC2-PPV-3104554</t>
+  </si>
+  <si>
+    <t>2.33 GB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:02dae289541a70aa8de176626ac27b128b6e176a</t>
+  </si>
+  <si>
+    <t>FC2-PPV-3143345</t>
+  </si>
+  <si>
+    <t>6.60 GB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:03168be24ab5bd28229d926a2b5f70ebc578afec</t>
+  </si>
+  <si>
+    <t>FC2-PPV-2742024</t>
+  </si>
+  <si>
+    <t>1.75 GB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0325903abd0b32428e7fe031619e9e65c5869f81</t>
+  </si>
+  <si>
+    <t>FC2-PPV-4548658</t>
+  </si>
+  <si>
+    <t>1.90 GB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0336c9c0659ba0f29d4083b0bd4fea45c1b9739a</t>
+  </si>
+  <si>
+    <t>FC2-PPV-4320239</t>
+  </si>
+  <si>
+    <t>1.08 GB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:033e00742f7ddeb5d85bed53e656e3184cf3227e</t>
+  </si>
+  <si>
+    <t>FC2-PPV-4515229</t>
+  </si>
+  <si>
+    <t>3.29 GB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:034733c3a33f9a68997a49f53cf4f0805aa83745</t>
+  </si>
+  <si>
+    <t>FC2-PPV-4303407</t>
+  </si>
+  <si>
+    <t>6.83 GB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:03a732c34106e80716662e9145f61c2e4f90a9f2</t>
+  </si>
+  <si>
+    <t>FC2-PPV-2654794</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0406a5b58ce363698b934efddaf858f093def615</t>
+  </si>
+  <si>
+    <t>FC2-PPV-3137443</t>
+  </si>
+  <si>
+    <t>1.76 GB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:041cdef240940af4b9d9948352a1a0da474fb686</t>
+  </si>
+  <si>
+    <t>FC2-PPV-4362454</t>
+  </si>
+  <si>
+    <t>464.26 MB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:042825b6ebac84b2d491a201af2e41154a7fab74</t>
+  </si>
+  <si>
+    <t>FC2-PPV-2678828</t>
+  </si>
+  <si>
+    <t>3.39 GB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:04348f9faf1011b1308364372f285141f60184db</t>
+  </si>
+  <si>
+    <t>FC2-PPV-4312219</t>
+  </si>
+  <si>
+    <t>3.67 GB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0442f6263537eb83baa4d0d6afc165944a03372f</t>
+  </si>
+  <si>
+    <t>FC2-PPV-4198883</t>
+  </si>
+  <si>
+    <t>3.82 GB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:048866cbe02b8bfcb8a1379a1a7716a4d046f603</t>
+  </si>
+  <si>
+    <t>FC2-PPV-3088699</t>
+  </si>
+  <si>
+    <t>8.52 GB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:04aaaf2dbc03a28a0ac6e56226f71b3631a712a8</t>
+  </si>
+  <si>
+    <t>FC2-PPV-2589219</t>
+  </si>
+  <si>
+    <t>5.15 GB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:04be1446e7bf826722266acd81dea00fb90a2eff</t>
+  </si>
+  <si>
+    <t>FC2-PPV-4431682</t>
+  </si>
+  <si>
+    <t>5.86 GB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:04c245b1afbd4964636eaa9200027b43bb802d48</t>
+  </si>
+  <si>
+    <t>FC2-PPV-3092252</t>
+  </si>
+  <si>
+    <t>9.04 GB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:04cddec7cdaccddd7452234900290568985a0761</t>
+  </si>
+  <si>
+    <t>FC2-PPV-4524212</t>
+  </si>
+  <si>
+    <t>5.87 GB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:04eb3f0e993c8e18e3978c9d20b5e3ae017e667e</t>
+  </si>
+  <si>
+    <t>FC2-PPV-4339388</t>
+  </si>
+  <si>
+    <t>7.09 GB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:04fe15b15e7217b85c17a34b8393904e8710231e</t>
+  </si>
+  <si>
+    <t>FC2-PPV-3079995</t>
+  </si>
+  <si>
+    <t>7.24 GB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:050e425d6f2c4b8e3a13bb7aa4b7261caa6ecc15</t>
+  </si>
+  <si>
+    <t>FC2-PPV-4590421</t>
+  </si>
+  <si>
+    <t>2.53 GB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:050e8c6c81a5ea9d4d9c714e8a9c8bc525b122a9</t>
+  </si>
+  <si>
+    <t>FC2-PPV-4507809</t>
+  </si>
+  <si>
+    <t>812.76 MB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:05172f349cc9a5e80680a63a3dc1c4ea14cd9a2b</t>
+  </si>
+  <si>
+    <t>FC2-PPV-4545236</t>
+  </si>
+  <si>
+    <t>6.35 GB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:055b64d739e627050dc1933a97580796c889e42d</t>
+  </si>
+  <si>
+    <t>FC2-PPV-4411794</t>
+  </si>
+  <si>
+    <t>5.29 GB</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0575a260fb377cd4904a4b5ad9d4b1ccf38fd465</t>
   </si>
   <si>
     <t>Error</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:cc693db3efceaabd5590ce209bfee30ece36dc82</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:77d199c5cbc539ca08c7df737e189d1838e24115</t>
-  </si>
-  <si>
-    <t>FC2-PPV-2956191</t>
-  </si>
-  <si>
-    <t>4.99 GB</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:263f8e4cc19333c99a950db2574c238907cf0f4a</t>
-  </si>
-  <si>
-    <t>FC2-PPV-2956158</t>
-  </si>
-  <si>
-    <t>5.78 GB</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:bb2f4bbe37965b1b18ed240c6c65416caea994c0</t>
-  </si>
-  <si>
-    <t>FC2-PPV-2956150</t>
-  </si>
-  <si>
-    <t>1.16 GB</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:9f30124578c72618045d4792b33315f1c1d4298a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:ea30bfb71dbab2c03b5781ee534c8407f71d74f5</t>
-  </si>
-  <si>
-    <t>FC2-PPV-2951004</t>
-  </si>
-  <si>
-    <t>1.55 GB</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:6d56c47525671835cd7b721a6f4e52d99edc1879</t>
-  </si>
-  <si>
-    <t>FC2-PPV-2950995</t>
-  </si>
-  <si>
-    <t>1.69 GB</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:81b36ef46fb428791c48fe314d99720e77db45de</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:8dc876d6efaf905fdd138465e22182e09afd0fb8</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:77282968c1803cb5133f3152041028d2ccaa18ec</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4a95ee047ab5a34644b68957947b1f48202226bb</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:7c98c5ce1dec3be3216a3ffb5a23db016de4829c</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c7759b88bba94c91a978cd461d904574643a6c2d</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:e4d6fcfd5fcbfbe98e00fe58e8e992912cfe2b03</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:53729a209c7b73b325927500819ba7be44946c5a</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3f7c5c567b22133c5da901b887e551c44a72d8dd</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:a5ec7b462606ce91bf225c4dbfaadb495922d45f</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:696743d21fb4f311fd0f6ae9e514ee4ed3f70c28</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:6fde6150de80344755b0202e7ec8388e81708aa5</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:72dc3057d255f8969a3ef82992fd15473d4482b4</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:eae985e104db0d49c010e7c97c99571fb9575303</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:22472800e70dcd541ae12767064a651367d988e8</t>
-  </si>
-  <si>
-    <t>FC2-PPV-2961714</t>
-  </si>
-  <si>
-    <t>450.02 MB</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:6f26c05901eed1cbcbe22f53a38ab8772bc08eec</t>
-  </si>
-  <si>
-    <t>FC2-PPV-2935056</t>
-  </si>
-  <si>
-    <t>973.74 MB</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:f75360953fb709205bb71cebb3ce1493087c62ff</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:a59342610f08a885ccebe73e41cdf24758efac1a</t>
-  </si>
-  <si>
-    <t>FC2-PPV-2887705</t>
-  </si>
-  <si>
-    <t>500.23 MB</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:065337f73cdb8671e1aec0ba2c2d0a97c3dbe486</t>
-  </si>
-  <si>
-    <t>FC2-PPV-2965308</t>
-  </si>
-  <si>
-    <t>1.57 GB</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3850dcf28adee18aa46c1dfb1790b6252385e26f</t>
-  </si>
-  <si>
-    <t>FC2-PPV-2964281</t>
-  </si>
-  <si>
-    <t>1.85 GB</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:a157b2fb165bc67fd1ca84621e069e8724503284</t>
-  </si>
-  <si>
-    <t>FC2-PPV-2962157</t>
-  </si>
-  <si>
-    <t>3.12 GB</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:27282222bab8932f9250c3ba10f55ed661c2062a</t>
-  </si>
-  <si>
-    <t>FC2-PPV-2961792</t>
-  </si>
-  <si>
-    <t>2.05 GB</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:01b4d50b9cafb2c2343498cd56969ce71c8d85af</t>
-  </si>
-  <si>
-    <t>FC2-PPV-2961763</t>
-  </si>
-  <si>
-    <t>2.02 GB</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:73a301fe06286ffb413052b9d3417931eba56e19</t>
-  </si>
-  <si>
-    <t>FC2-PPV-2953394</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:c84daf17da1fd06f7156117bcfa1748ae2df75bd</t>
-  </si>
-  <si>
-    <t>FC2-PPV-2962429</t>
-  </si>
-  <si>
-    <t>430.79 MB</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:9aa519488b4cf6e09b44556e2640da66ce4065d9</t>
-  </si>
-  <si>
-    <t>FC2-PPV-2964827</t>
-  </si>
-  <si>
-    <t>2.16 GB</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5006581550ba669f0dca45cf001d353017da4d35</t>
-  </si>
-  <si>
-    <t>FC2-PPV-2968096</t>
-  </si>
-  <si>
-    <t>692.10 MB</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:cb43e859532cdc88f3110d41b260078c4d1a3fc9</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:eed214183beec5b71033150a2eed2dd8d0e7e55a</t>
-  </si>
-  <si>
-    <t>FC2-PPV-2969559</t>
-  </si>
-  <si>
-    <t>1.97 GB</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0e0eefb7d4a4ce0c4ce252afbaf0384ed9f4f280</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:864e8445b8c7d7a1d9e878c5f6bf08c06aac43a8</t>
-  </si>
-  <si>
-    <t>FC2-PPV-2967468</t>
-  </si>
-  <si>
-    <t>3.44 GB</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:66710b6829f6551fc24d60a227889779935b27c4</t>
-  </si>
-  <si>
-    <t>FC2-PPV-2965312</t>
-  </si>
-  <si>
-    <t>2.95 GB</t>
+    <t>magnet:?xt=urn:btih:05959cfd355f10c64058aa25cdc3173def7971d8</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:05bc92f0993dfa6cf6aedfdf8f03ad4df06f6af7</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:05dc8c6c0ffbfdef34afabcde28a9e8154d5cffe</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:0610d139644dab898cf2b601e537030965cdc927</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:061f249ff521d4cc8f45709649a944eb4621387f</t>
+  </si>
+  <si>
+    <t>magnet:?xt=urn:btih:062d403517018cf1e8692bceb3c93cde2b8bb668</t>
   </si>
 </sst>
 </file>
@@ -329,7 +497,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="tmpomiq8wf7.jpg"/>
+        <xdr:cNvPr id="2" name="Picture 1" descr="tmpst5vewx7.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -367,7 +535,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2" descr="tmpi8kjcmoz.jpg"/>
+        <xdr:cNvPr id="3" name="Picture 2" descr="tmp1o10omj_.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -405,7 +573,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3" descr="tmpqk0fxzt_.jpg"/>
+        <xdr:cNvPr id="4" name="Picture 3" descr="tmplae14qdo.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -443,7 +611,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4" descr="tmp30ccqo73.jpg"/>
+        <xdr:cNvPr id="5" name="Picture 4" descr="tmp0c2qq_mq.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -481,7 +649,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5" descr="tmpwmnl1yhx.jpg"/>
+        <xdr:cNvPr id="6" name="Picture 5" descr="tmpnmmhew8q.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -519,7 +687,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 6" descr="tmp1nng_xlp.jpg"/>
+        <xdr:cNvPr id="7" name="Picture 6" descr="tmpnj05k36v.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -557,7 +725,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 7" descr="tmp0hz33g7w.jpg"/>
+        <xdr:cNvPr id="8" name="Picture 7" descr="tmp_8oaz1_k.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -595,7 +763,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 8" descr="tmpk2uqctlb.jpg"/>
+        <xdr:cNvPr id="9" name="Picture 8" descr="tmpeml62j0_.jpg"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -620,6 +788,82 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9" descr="tmpmmk5ee7a.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21669375" y="10620375"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 10" descr="tmpepw3m5qy.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27051000" y="10620375"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>5</xdr:row>
@@ -633,13 +877,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 9" descr="tmp895ggvju.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <xdr:cNvPr id="12" name="Picture 11" descr="tmpvuw4qptd.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -671,13 +915,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Picture 10" descr="tmploc8tubn.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <xdr:cNvPr id="13" name="Picture 12" descr="tmp7w8gi6nb.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -709,13 +953,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Picture 11" descr="tmponrk1rtn.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <xdr:cNvPr id="14" name="Picture 13" descr="tmp21nlkkft.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -747,13 +991,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="Picture 12" descr="tmp7we8vumy.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <xdr:cNvPr id="15" name="Picture 14" descr="tmpmxy04xj7.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -785,13 +1029,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Picture 13" descr="tmpoeotk9_n.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <xdr:cNvPr id="16" name="Picture 15" descr="tmpqrbepnkb.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -812,31 +1056,31 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>714375</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>3429000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="Picture 14" descr="tmpj1dg6rvq.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5524500" y="21050250"/>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="Picture 16" descr="tmpkjca7r9g.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5524500" y="17573625"/>
           <a:ext cx="6096000" cy="3429000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -850,31 +1094,31 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>714375</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>3429000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="Picture 15" descr="tmp8ky6nabf.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10906125" y="21050250"/>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="Picture 17" descr="tmpv9xb6e35.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10906125" y="17573625"/>
           <a:ext cx="6096000" cy="3429000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -888,31 +1132,31 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>714375</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>3429000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="Picture 16" descr="tmpnw5sjkm2.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="16287750" y="21050250"/>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="Picture 18" descr="tmpo3zi0st9.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16287750" y="17573625"/>
           <a:ext cx="6096000" cy="3429000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -926,31 +1170,31 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>714375</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>3429000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="Picture 17" descr="tmpfc9szvwe.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="21669375" y="21050250"/>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="Picture 19" descr="tmpv6yyt8ar.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21669375" y="17573625"/>
           <a:ext cx="6096000" cy="3429000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -964,31 +1208,31 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>3429000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="19" name="Picture 18" descr="tmpefemrlu_.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="27051000" y="21050250"/>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="Picture 20" descr="tmpi875cti1.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27051000" y="17573625"/>
           <a:ext cx="6096000" cy="3429000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1013,13 +1257,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="20" name="Picture 19" descr="tmp_h0degec.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
+        <xdr:cNvPr id="22" name="Picture 21" descr="tmpvspyhcc4.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1051,13 +1295,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="21" name="Picture 20" descr="tmpotm3021i.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
+        <xdr:cNvPr id="23" name="Picture 22" descr="tmp4q4vydi_.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1089,13 +1333,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="22" name="Picture 21" descr="tmpg_dxnvil.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
+        <xdr:cNvPr id="24" name="Picture 23" descr="tmphf2pdqsw.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1127,13 +1371,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="23" name="Picture 22" descr="tmp148trosg.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
+        <xdr:cNvPr id="25" name="Picture 24" descr="tmpq59wig8e.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1165,13 +1409,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="24" name="Picture 23" descr="tmp4kzmrl05.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
+        <xdr:cNvPr id="26" name="Picture 25" descr="tmps1jicvfs.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1192,6 +1436,2020 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="27" name="Picture 26" descr="tmp6gz_ghm7.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5524500" y="28003500"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="28" name="Picture 27" descr="tmpjs7v6il3.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10906125" y="28003500"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="29" name="Picture 28" descr="tmpz0fjx20c.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16287750" y="28003500"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="30" name="Picture 29" descr="tmpj26znkpj.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId29"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21669375" y="28003500"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="31" name="Picture 30" descr="tmpdgkzie6x.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId30"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27051000" y="28003500"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="32" name="Picture 31" descr="tmp3nmu825t.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId31"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5524500" y="31480125"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="33" name="Picture 32" descr="tmpqgbtw9k6.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId32"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10906125" y="31480125"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="34" name="Picture 33" descr="tmpdrtt2o9n.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16287750" y="31480125"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="35" name="Picture 34" descr="tmpakbv2obx.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId34"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21669375" y="31480125"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="36" name="Picture 35" descr="tmplgxuxil8.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId35"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27051000" y="31480125"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="37" name="Picture 36" descr="tmp76bi23qd.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId36"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5524500" y="34956750"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="38" name="Picture 37" descr="tmpyqjqxv7f.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId37"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10906125" y="34956750"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="39" name="Picture 38" descr="tmpbo1mw9c_.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId38"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16287750" y="34956750"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="40" name="Picture 39" descr="tmpkvycir_x.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId39"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5524500" y="38433375"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="41" name="Picture 40" descr="tmpmcjfrk7d.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId40"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10906125" y="38433375"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="42" name="Picture 41" descr="tmpgk31y5l5.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId41"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16287750" y="38433375"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="43" name="Picture 42" descr="tmps2lzvugh.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId42"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21669375" y="38433375"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="44" name="Picture 43" descr="tmp15vbx3gf.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId43"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27051000" y="38433375"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="45" name="Picture 44" descr="tmpd9qva29k.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId44"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5524500" y="41910000"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="46" name="Picture 45" descr="tmpaeoqqnxt.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId45"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10906125" y="41910000"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="47" name="Picture 46" descr="tmp4ppd9qna.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId46"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16287750" y="41910000"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="48" name="Picture 47" descr="tmp9vcbvmp2.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId47"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21669375" y="41910000"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="49" name="Picture 48" descr="tmpa0if4ju7.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId48"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27051000" y="41910000"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="50" name="Picture 49" descr="tmpoh9ys29g.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId49"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5524500" y="45386625"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="51" name="Picture 50" descr="tmpqy2uy7of.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId50"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10906125" y="45386625"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="52" name="Picture 51" descr="tmpw1kv2vmc.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId51"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16287750" y="45386625"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="53" name="Picture 52" descr="tmpmia7ke28.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId52"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21669375" y="45386625"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="54" name="Picture 53" descr="tmp0z41vymi.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId53"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27051000" y="45386625"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="55" name="Picture 54" descr="tmp4_iwjbg1.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId54"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5524500" y="48863250"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="56" name="Picture 55" descr="tmpajr8hxzu.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId54"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10906125" y="48863250"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="57" name="Picture 56" descr="tmpk5fepxkp.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId54"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16287750" y="48863250"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="58" name="Picture 57" descr="tmpw43qdyom.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId55"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5524500" y="52339875"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="59" name="Picture 58" descr="tmpzaj0cmne.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId56"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10906125" y="52339875"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="60" name="Picture 59" descr="tmpp0vtkob_.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId57"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16287750" y="52339875"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="61" name="Picture 60" descr="tmpnbpwqepr.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId58"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21669375" y="52339875"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="62" name="Picture 61" descr="tmpppsuca96.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId59"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27051000" y="52339875"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="63" name="Picture 62" descr="tmph606m7gt.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId60"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5524500" y="59293125"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="64" name="Picture 63" descr="tmpigjjin_o.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId61"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10906125" y="59293125"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="65" name="Picture 64" descr="tmpi6_ofcii.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId62"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16287750" y="59293125"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="66" name="Picture 65" descr="tmpnvlw6kb3.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId63"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21669375" y="59293125"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="67" name="Picture 66" descr="tmpcsx73dh8.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId64"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27051000" y="59293125"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="68" name="Picture 67" descr="tmpp26m95v7.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId65"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5524500" y="62769750"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="69" name="Picture 68" descr="tmpqrjsk4gk.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId66"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10906125" y="62769750"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="70" name="Picture 69" descr="tmprvak6fs4.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId67"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16287750" y="62769750"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="71" name="Picture 70" descr="tmpnx80fkqz.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId68"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21669375" y="62769750"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="72" name="Picture 71" descr="tmpojr1ss32.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId69"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27051000" y="62769750"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="73" name="Picture 72" descr="tmpgyllsatx.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId70"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5524500" y="66246375"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="74" name="Picture 73" descr="tmpeylfmoa9.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId71"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10906125" y="66246375"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="75" name="Picture 74" descr="tmpaj7_gqcj.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId72"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16287750" y="66246375"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="76" name="Picture 75" descr="tmpmk9r_u9e.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId73"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21669375" y="66246375"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="77" name="Picture 76" descr="tmpxmj0atew.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId74"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27051000" y="66246375"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="78" name="Picture 77" descr="tmprt89lzkw.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId75"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5524500" y="69723000"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="79" name="Picture 78" descr="tmpx4gfulkw.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId76"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10906125" y="69723000"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
@@ -1203,13 +3461,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="25" name="Picture 24" descr="tmp0v0znkba.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
+        <xdr:cNvPr id="80" name="Picture 79" descr="tmp73u2lm55.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId77"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1241,13 +3499,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="26" name="Picture 25" descr="tmpo6s14ad0.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
+        <xdr:cNvPr id="81" name="Picture 80" descr="tmp6ppgolkv.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId78"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1279,13 +3537,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="27" name="Picture 26" descr="tmphn_4twoo.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22"/>
+        <xdr:cNvPr id="82" name="Picture 81" descr="tmptdx05l6k.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId79"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1317,13 +3575,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="28" name="Picture 27" descr="tmp32c00ykz.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
+        <xdr:cNvPr id="83" name="Picture 82" descr="tmprwo0jw5u.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId80"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1355,13 +3613,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="29" name="Picture 28" descr="tmpz645a80j.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24"/>
+        <xdr:cNvPr id="84" name="Picture 83" descr="tmp7oei9wxa.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId81"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1393,13 +3651,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="30" name="Picture 29" descr="tmpc17i8cc7.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25"/>
+        <xdr:cNvPr id="85" name="Picture 84" descr="tmpzfs88f9s.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId82"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1431,13 +3689,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="31" name="Picture 30" descr="tmpaindggok.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26"/>
+        <xdr:cNvPr id="86" name="Picture 85" descr="tmppkrhl7d4.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId83"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1469,13 +3727,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="32" name="Picture 31" descr="tmpu17ump2o.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27"/>
+        <xdr:cNvPr id="87" name="Picture 86" descr="tmp8q5e1o_m.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId84"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1507,13 +3765,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="33" name="Picture 32" descr="tmpvxmer4mw.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28"/>
+        <xdr:cNvPr id="88" name="Picture 87" descr="tmpdb6xrcdc.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId85"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1545,13 +3803,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="34" name="Picture 33" descr="tmp4b5idetp.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId29"/>
+        <xdr:cNvPr id="89" name="Picture 88" descr="tmp31ugci0e.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId86"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1583,13 +3841,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="35" name="Picture 34" descr="tmpqlqzr0ox.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId30"/>
+        <xdr:cNvPr id="90" name="Picture 89" descr="tmpkfivhhw1.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId87"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1621,13 +3879,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="36" name="Picture 35" descr="tmpo5ra8k2t.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId31"/>
+        <xdr:cNvPr id="91" name="Picture 90" descr="tmp2ail7tyh.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId88"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1659,13 +3917,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="37" name="Picture 36" descr="tmp7iq_wkhq.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId32"/>
+        <xdr:cNvPr id="92" name="Picture 91" descr="tmp20ku1pot.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId89"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1697,13 +3955,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="38" name="Picture 37" descr="tmpl6sklm3p.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33"/>
+        <xdr:cNvPr id="93" name="Picture 92" descr="tmpfkqw6wjh.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId90"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1735,13 +3993,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="39" name="Picture 38" descr="tmpn4hccr_j.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId34"/>
+        <xdr:cNvPr id="94" name="Picture 93" descr="tmphq23ayy1.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId91"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1762,31 +4020,31 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>714375</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>3429000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="40" name="Picture 39" descr="tmph0b89s90.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId35"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5524500" y="94059375"/>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="95" name="Picture 94" descr="tmp1pbrr8_9.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId92"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5524500" y="90582750"/>
           <a:ext cx="6096000" cy="3429000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1800,31 +4058,31 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>714375</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>3429000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="41" name="Picture 40" descr="tmpl0zf4i_o.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId36"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10906125" y="94059375"/>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="96" name="Picture 95" descr="tmpo1vc4_1o.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId93"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10906125" y="90582750"/>
           <a:ext cx="6096000" cy="3429000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1838,31 +4096,31 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>714375</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>3429000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="42" name="Picture 41" descr="tmptl8fzb3e.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId37"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="16287750" y="94059375"/>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="97" name="Picture 96" descr="tmpzrmgiddw.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId94"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16287750" y="90582750"/>
           <a:ext cx="6096000" cy="3429000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1876,31 +4134,31 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>714375</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>3429000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="43" name="Picture 42" descr="tmpvp9fvldh.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId38"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="21669375" y="94059375"/>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="98" name="Picture 97" descr="tmp2y87pba6.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId95"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21669375" y="90582750"/>
           <a:ext cx="6096000" cy="3429000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1914,31 +4172,31 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>3429000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="44" name="Picture 43" descr="tmpoy8sgdzi.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId39"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="27051000" y="94059375"/>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="99" name="Picture 98" descr="tmph44c6ccp.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId96"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27051000" y="90582750"/>
           <a:ext cx="6096000" cy="3429000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1963,13 +4221,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="45" name="Picture 44" descr="tmpgo4w9kl9.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId40"/>
+        <xdr:cNvPr id="100" name="Picture 99" descr="tmpa5w29lsp.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId97"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2001,13 +4259,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="46" name="Picture 45" descr="tmp_k7ex22o.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId41"/>
+        <xdr:cNvPr id="101" name="Picture 100" descr="tmpif_dngxv.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId98"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2039,13 +4297,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="47" name="Picture 46" descr="tmpzhkhv7kf.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId42"/>
+        <xdr:cNvPr id="102" name="Picture 101" descr="tmpfzacj10x.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId99"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2077,13 +4335,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="48" name="Picture 47" descr="tmp_t7fdt10.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId43"/>
+        <xdr:cNvPr id="103" name="Picture 102" descr="tmplbt5t4dc.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId100"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2115,13 +4373,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="Picture 48" descr="tmphl17d_zg.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId44"/>
+        <xdr:cNvPr id="104" name="Picture 103" descr="tmph0nqfoe2.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId101"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2142,31 +4400,31 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>714375</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>3429000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Picture 49" descr="tmpuy4iomwz.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId45"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5524500" y="101012625"/>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="105" name="Picture 104" descr="tmp5ua6kdl3.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId102"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5524500" y="104489250"/>
           <a:ext cx="6096000" cy="3429000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2180,31 +4438,31 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>714375</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>3429000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="51" name="Picture 50" descr="tmp8v679x4c.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId46"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10906125" y="101012625"/>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="106" name="Picture 105" descr="tmp7e23zpna.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId103"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10906125" y="104489250"/>
           <a:ext cx="6096000" cy="3429000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2218,31 +4476,31 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>714375</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>3429000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="52" name="Picture 51" descr="tmp_huhn5wj.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId47"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="16287750" y="101012625"/>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="107" name="Picture 106" descr="tmp4b0c_c35.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId104"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16287750" y="104489250"/>
           <a:ext cx="6096000" cy="3429000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2256,31 +4514,31 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>714375</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>3429000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="53" name="Picture 52" descr="tmp9ipx1ge6.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId48"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="21669375" y="101012625"/>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="108" name="Picture 107" descr="tmpotm7lu0a.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId105"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21669375" y="104489250"/>
           <a:ext cx="6096000" cy="3429000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2294,31 +4552,31 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>3429000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="54" name="Picture 53" descr="tmp_2imosfs.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId49"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="27051000" y="101012625"/>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="109" name="Picture 108" descr="tmp0afbmyd4.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId106"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27051000" y="104489250"/>
           <a:ext cx="6096000" cy="3429000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2332,183 +4590,145 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>714375</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>3429000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="55" name="Picture 54" descr="tmpeik7kck_.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId50"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5524500" y="104489250"/>
-          <a:ext cx="6096000" cy="3429000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="110" name="Picture 109" descr="tmp7xl6kecg.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId107"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5524500" y="107965875"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="111" name="Picture 110" descr="tmp_m0bu3wb.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId108"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5524500" y="114919125"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>714375</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>3429000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="56" name="Picture 55" descr="tmpkcw2nuiy.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId51"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10906125" y="104489250"/>
-          <a:ext cx="6096000" cy="3429000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>714375</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>3429000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="57" name="Picture 56" descr="tmpd0s3243e.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId52"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5524500" y="107965875"/>
-          <a:ext cx="6096000" cy="3429000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="112" name="Picture 111" descr="tmps8etcgvp.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId109"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10906125" y="114919125"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>714375</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>3429000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="58" name="Picture 57" descr="tmp_uyfv6t7.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId53"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10906125" y="107965875"/>
-          <a:ext cx="6096000" cy="3429000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>714375</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>3429000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="59" name="Picture 58" descr="tmpsb1ew3en.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId52"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="16287750" y="107965875"/>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="113" name="Picture 112" descr="tmpteyywgte.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId110"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16287750" y="114919125"/>
           <a:ext cx="6096000" cy="3429000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2522,214 +4742,24 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>714375</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>3429000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="60" name="Picture 59" descr="tmpejb6e61y.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId53"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="21669375" y="107965875"/>
-          <a:ext cx="6096000" cy="3429000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>3429000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="61" name="Picture 60" descr="tmpb_t7w5aq.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId52"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="27051000" y="107965875"/>
-          <a:ext cx="6096000" cy="3429000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>714375</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>3429000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="62" name="Picture 61" descr="tmp1nluxb21.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId54"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5524500" y="114919125"/>
-          <a:ext cx="6096000" cy="3429000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>714375</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>3429000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="63" name="Picture 62" descr="tmpq_ehoxq6.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId55"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10906125" y="114919125"/>
-          <a:ext cx="6096000" cy="3429000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>714375</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>3429000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="64" name="Picture 63" descr="tmp47yl2xg7.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId56"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="16287750" y="114919125"/>
-          <a:ext cx="6096000" cy="3429000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>714375</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>3429000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="65" name="Picture 64" descr="tmpqdk25eiy.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId57"/>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="114" name="Picture 113" descr="tmpgexj3aek.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId111"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2761,13 +4791,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="66" name="Picture 65" descr="tmphvtbq8s8.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId58"/>
+        <xdr:cNvPr id="115" name="Picture 114" descr="tmpaytkkgwh.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId112"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2788,31 +4818,31 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>714375</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>3429000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="67" name="Picture 66" descr="tmpnvxc7gu_.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId59"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5524500" y="125349000"/>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="116" name="Picture 115" descr="tmpi0fazbtr.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId113"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5524500" y="118395750"/>
           <a:ext cx="6096000" cy="3429000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2826,31 +4856,31 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>714375</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>3429000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="68" name="Picture 67" descr="tmpzax7t27v.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId60"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10906125" y="125349000"/>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="117" name="Picture 116" descr="tmpk360cick.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId114"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10906125" y="118395750"/>
           <a:ext cx="6096000" cy="3429000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2864,31 +4894,31 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>714375</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>3429000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="69" name="Picture 68" descr="tmpswwk5r_4.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId61"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="16287750" y="125349000"/>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="118" name="Picture 117" descr="tmpy3boydfd.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId115"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16287750" y="118395750"/>
           <a:ext cx="6096000" cy="3429000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2902,31 +4932,31 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>714375</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>3429000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="70" name="Picture 69" descr="tmpns4uafen.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId62"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="21669375" y="125349000"/>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="119" name="Picture 118" descr="tmpc6xr_kwd.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId116"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21669375" y="118395750"/>
           <a:ext cx="6096000" cy="3429000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2940,31 +4970,31 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>3429000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="71" name="Picture 70" descr="tmpb5yqobxh.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId63"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="27051000" y="125349000"/>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="120" name="Picture 119" descr="tmpcu75rlkh.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId117"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27051000" y="118395750"/>
           <a:ext cx="6096000" cy="3429000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2978,31 +5008,31 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>714375</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>3429000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="72" name="Picture 71" descr="tmpj6ndv64u.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId64"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5524500" y="132302250"/>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="121" name="Picture 120" descr="tmpi7h_3uav.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId118"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5524500" y="121872375"/>
           <a:ext cx="6096000" cy="3429000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3016,31 +5046,31 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>714375</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>3429000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="73" name="Picture 72" descr="tmp9n5xu25j.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId65"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10906125" y="132302250"/>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="122" name="Picture 121" descr="tmp5sorip8r.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId119"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10906125" y="121872375"/>
           <a:ext cx="6096000" cy="3429000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3054,31 +5084,31 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>714375</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>3429000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="74" name="Picture 73" descr="tmpkmd0l_oz.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId66"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="16287750" y="132302250"/>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="123" name="Picture 122" descr="tmprzmwsmkv.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId120"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16287750" y="121872375"/>
           <a:ext cx="6096000" cy="3429000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3092,31 +5122,31 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>714375</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>3429000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="75" name="Picture 74" descr="tmpq6v3k62g.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId67"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="21669375" y="132302250"/>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="124" name="Picture 123" descr="tmpj07fx9t6.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId118"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21669375" y="121872375"/>
           <a:ext cx="6096000" cy="3429000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3130,31 +5160,31 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>3429000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="76" name="Picture 75" descr="tmpeg6paglz.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId68"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="27051000" y="132302250"/>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="125" name="Picture 124" descr="tmpp_vsubj1.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId119"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27051000" y="121872375"/>
           <a:ext cx="6096000" cy="3429000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3168,6 +5198,120 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="126" name="Picture 125" descr="tmp66jvapdj.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId121"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5524500" y="125349000"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="127" name="Picture 126" descr="tmpl5noetzi.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId122"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10906125" y="125349000"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="128" name="Picture 127" descr="tmp5sk0tjp4.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId123"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16287750" y="125349000"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>40</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
@@ -3179,13 +5323,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="77" name="Picture 76" descr="tmpyyxayiob.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId69"/>
+        <xdr:cNvPr id="129" name="Picture 128" descr="tmppug7c2c2.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId124"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3217,13 +5361,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="78" name="Picture 77" descr="tmpk5jwov1m.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId69"/>
+        <xdr:cNvPr id="130" name="Picture 129" descr="tmp9w3n72g4.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId125"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3255,13 +5399,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="79" name="Picture 78" descr="tmp9yyvy2_g.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId69"/>
+        <xdr:cNvPr id="131" name="Picture 130" descr="tmpnzs5rzkh.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId126"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3293,13 +5437,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="80" name="Picture 79" descr="tmpsfb1i0s8.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId70"/>
+        <xdr:cNvPr id="132" name="Picture 131" descr="tmp89pystd4.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId127"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3331,13 +5475,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="81" name="Picture 80" descr="tmp89_gjj7q.jpg"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId71"/>
+        <xdr:cNvPr id="133" name="Picture 132" descr="tmpo5ra7x41.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId128"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3345,6 +5489,576 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="27051000" y="135778875"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="134" name="Picture 133" descr="tmpm42ez1ev.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId129"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5524500" y="139255500"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="135" name="Picture 134" descr="tmp1fe75kc9.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId130"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10906125" y="139255500"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="136" name="Picture 135" descr="tmplwhexls7.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId131"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16287750" y="139255500"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="137" name="Picture 136" descr="tmp9gof9cyc.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId132"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21669375" y="139255500"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="138" name="Picture 137" descr="tmpoji1cp2n.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId133"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27051000" y="139255500"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="139" name="Picture 138" descr="tmplzyk8q44.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId134"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5524500" y="142732125"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="140" name="Picture 139" descr="tmp13ejlnrr.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId135"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10906125" y="142732125"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="141" name="Picture 140" descr="tmp5edt6fh6.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId136"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16287750" y="142732125"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="142" name="Picture 141" descr="tmp00z1om46.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId137"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21669375" y="142732125"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="143" name="Picture 142" descr="tmphon7w8vj.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId138"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27051000" y="142732125"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="144" name="Picture 143" descr="tmpywj2lf55.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId139"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5524500" y="146208750"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="145" name="Picture 144" descr="tmpzukbdlhr.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId140"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10906125" y="146208750"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="146" name="Picture 145" descr="tmpfvs8uw3v.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId141"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16287750" y="146208750"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="147" name="Picture 146" descr="tmpjmgtfx_u.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId142"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21669375" y="146208750"/>
+          <a:ext cx="6096000" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>3429000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="148" name="Picture 147" descr="tmp20m9qj6u.jpg"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId143"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27051000" y="146208750"/>
           <a:ext cx="6096000" cy="3429000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3642,7 +6356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="20.7109375" customWidth="1"/>
@@ -3670,437 +6384,655 @@
       <c r="B2" t="s">
         <v>5</v>
       </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="3" spans="1:4" ht="274" customHeight="1">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="274" customHeight="1">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="274" customHeight="1">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="274" customHeight="1">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="274" customHeight="1">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>20</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="274" customHeight="1">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="274" customHeight="1">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C9">
         <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="274" customHeight="1">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>29</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="274" customHeight="1">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>5</v>
+        <v>32</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="274" customHeight="1">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>5</v>
+        <v>35</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="274" customHeight="1">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>5</v>
+        <v>38</v>
+      </c>
+      <c r="C13">
+        <v>3</v>
+      </c>
+      <c r="D13" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="274" customHeight="1">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>5</v>
+        <v>41</v>
+      </c>
+      <c r="C14">
+        <v>3</v>
+      </c>
+      <c r="D14" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="274" customHeight="1">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>5</v>
+        <v>44</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="274" customHeight="1">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="B16" t="s">
-        <v>5</v>
+        <v>47</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="274" customHeight="1">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="B17" t="s">
-        <v>5</v>
+        <v>50</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="D17" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="274" customHeight="1">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="B18" t="s">
-        <v>5</v>
+        <v>53</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="274" customHeight="1">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="B19" t="s">
-        <v>5</v>
+        <v>56</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="274" customHeight="1">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="B20" t="s">
-        <v>5</v>
+        <v>59</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="274" customHeight="1">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="B21" t="s">
-        <v>5</v>
+        <v>62</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="274" customHeight="1">
       <c r="A22" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="B22" t="s">
-        <v>5</v>
+        <v>65</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="274" customHeight="1">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="B23" t="s">
-        <v>5</v>
+        <v>68</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="274" customHeight="1">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="B24" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="C24">
         <v>2</v>
       </c>
       <c r="D24" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="274" customHeight="1">
       <c r="A25" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="C25">
         <v>2</v>
       </c>
       <c r="D25" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="274" customHeight="1">
       <c r="A26" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="B26" t="s">
-        <v>5</v>
+        <v>77</v>
+      </c>
+      <c r="C26">
+        <v>3</v>
+      </c>
+      <c r="D26" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="274" customHeight="1">
       <c r="A27" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="C27">
         <v>2</v>
       </c>
       <c r="D27" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="274" customHeight="1">
       <c r="A28" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="B28" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="C28">
         <v>2</v>
       </c>
       <c r="D28" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="274" customHeight="1">
       <c r="A29" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="B29" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="C29">
         <v>2</v>
       </c>
       <c r="D29" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="274" customHeight="1">
       <c r="A30" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="B30" t="s">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="C30">
         <v>2</v>
       </c>
       <c r="D30" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="274" customHeight="1">
       <c r="A31" t="s">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="B31" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="C31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D31" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="274" customHeight="1">
       <c r="A32" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="B32" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="C32">
         <v>2</v>
       </c>
       <c r="D32" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="274" customHeight="1">
       <c r="A33" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="B33" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="C33">
         <v>2</v>
       </c>
       <c r="D33" t="s">
-        <v>15</v>
+        <v>98</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="274" customHeight="1">
       <c r="A34" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="B34" t="s">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="C34">
         <v>2</v>
       </c>
       <c r="D34" t="s">
-        <v>66</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="274" customHeight="1">
       <c r="A35" t="s">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="B35" t="s">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="C35">
         <v>2</v>
       </c>
       <c r="D35" t="s">
-        <v>69</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="274" customHeight="1">
       <c r="A36" t="s">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="B36" t="s">
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="C36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D36" t="s">
-        <v>72</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="274" customHeight="1">
       <c r="A37" t="s">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="B37" t="s">
-        <v>5</v>
+        <v>109</v>
+      </c>
+      <c r="C37">
+        <v>2</v>
+      </c>
+      <c r="D37" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="274" customHeight="1">
       <c r="A38" t="s">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="B38" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="C38">
         <v>2</v>
       </c>
       <c r="D38" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="274" customHeight="1">
       <c r="A39" t="s">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="B39" t="s">
-        <v>5</v>
+        <v>115</v>
+      </c>
+      <c r="C39">
+        <v>2</v>
+      </c>
+      <c r="D39" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="274" customHeight="1">
       <c r="A40" t="s">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="B40" t="s">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="C40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D40" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="274" customHeight="1">
       <c r="A41" t="s">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="B41" t="s">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="C41">
         <v>2</v>
       </c>
       <c r="D41" t="s">
-        <v>83</v>
+        <v>122</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="274" customHeight="1">
+      <c r="A42" t="s">
+        <v>123</v>
+      </c>
+      <c r="B42" t="s">
+        <v>124</v>
+      </c>
+      <c r="C42">
+        <v>2</v>
+      </c>
+      <c r="D42" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="274" customHeight="1">
+      <c r="A43" t="s">
+        <v>126</v>
+      </c>
+      <c r="B43" t="s">
+        <v>127</v>
+      </c>
+      <c r="C43">
+        <v>4</v>
+      </c>
+      <c r="D43" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="274" customHeight="1">
+      <c r="A44" t="s">
+        <v>129</v>
+      </c>
+      <c r="B44" t="s">
+        <v>130</v>
+      </c>
+      <c r="C44">
+        <v>2</v>
+      </c>
+      <c r="D44" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="274" customHeight="1">
+      <c r="A45" t="s">
+        <v>132</v>
+      </c>
+      <c r="B45" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="274" customHeight="1">
+      <c r="A46" t="s">
+        <v>134</v>
+      </c>
+      <c r="B46" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="274" customHeight="1">
+      <c r="A47" t="s">
+        <v>135</v>
+      </c>
+      <c r="B47" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="274" customHeight="1">
+      <c r="A48" t="s">
+        <v>136</v>
+      </c>
+      <c r="B48" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="274" customHeight="1">
+      <c r="A49" t="s">
+        <v>137</v>
+      </c>
+      <c r="B49" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="274" customHeight="1">
+      <c r="A50" t="s">
+        <v>138</v>
+      </c>
+      <c r="B50" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="274" customHeight="1">
+      <c r="A51" t="s">
+        <v>139</v>
+      </c>
+      <c r="B51" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>
